--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ULACIA ZKE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ULACIA ZKE.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>13.2435</v>
+        <v>13.7397</v>
       </c>
       <c r="E2" t="n">
-        <v>9.132899999999999</v>
+        <v>4.0626</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1106</v>
+        <v>9.677099999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3932</v>
+        <v>6.872400000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6136</v>
+        <v>2.7746</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7796</v>
+        <v>4.097799999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2277</v>
+        <v>8.158300000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1881</v>
+        <v>3.9031</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0396</v>
+        <v>4.2553</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8345</v>
+        <v>-1.2859</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4254</v>
+        <v>-1.1284</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.26</v>
+        <v>-0.1574</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0006</v>
+        <v>0.779</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.4004</v>
+        <v>-7.4</v>
       </c>
       <c r="R2" t="n">
-        <v>3.401</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>6.7095</v>
+        <v>9.941700000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4663</v>
+        <v>5.1658</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2433</v>
+        <v>4.7758</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8597</v>
+        <v>-3.8532</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1606</v>
+        <v>-1.8615</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6990999999999999</v>
+        <v>-1.9917</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.292</v>
+        <v>3.4067</v>
       </c>
       <c r="E3" t="n">
-        <v>5.375500000000001</v>
+        <v>1.226799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9166000000000001</v>
+        <v>2.1799</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0121</v>
+        <v>1.1918</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4141</v>
+        <v>1.7788</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5980000000000001</v>
+        <v>-0.5870999999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7454</v>
+        <v>0.3014999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5379999999999998</v>
+        <v>1.435</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2074</v>
+        <v>-1.1336</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7332999999999998</v>
+        <v>0.8902000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1239000000000001</v>
+        <v>0.3439000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6093999999999999</v>
+        <v>0.5464</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2009</v>
+        <v>-8.179</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2009</v>
+        <v>6.6211</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8204</v>
+        <v>4.5408</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4523</v>
+        <v>3.153799999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3681</v>
+        <v>1.3871</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4595</v>
+        <v>-0.768</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3787</v>
+        <v>5.9506</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.9191</v>
+        <v>-6.7185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LARRANAGA ORMAZABAL</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4.727</v>
+        <v>3.0632</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2898</v>
+        <v>3.0632</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4372</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7233</v>
+        <v>3.0632</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3568</v>
+        <v>1.8474</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3665</v>
+        <v>1.2158</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4616</v>
+        <v>3.0632</v>
       </c>
       <c r="K4" t="n">
-        <v>0.18</v>
+        <v>1.8474</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2817</v>
+        <v>1.2158</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2616</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1768</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0848</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4004</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9363</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6312</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3051</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5399</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7996</v>
+        <v>1.6414</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7996</v>
+        <v>3.2722</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.631</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7996</v>
+        <v>0.944</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1997</v>
+        <v>2.5067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5999</v>
+        <v>-1.5626</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7996</v>
+        <v>1.8096</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1997</v>
+        <v>2.2631</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5999</v>
+        <v>-0.4536</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.8655</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1091</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.06790000000000007</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.1833</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-1.1154</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.9021</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>P. ELOLA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6643</v>
+        <v>-0.1685</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3799</v>
+        <v>-1.4919</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2844</v>
+        <v>1.3234</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3091</v>
+        <v>1.2886</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1335</v>
+        <v>0.4411999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1756</v>
+        <v>0.8473999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9597</v>
+        <v>1.2107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9197</v>
+        <v>0.8621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.3486</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3494</v>
+        <v>0.07779999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2138</v>
+        <v>-0.421</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1356</v>
+        <v>0.4988</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>1.9473</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1552000000000001</v>
+        <v>0.2908</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4202</v>
+        <v>-1.0668</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.265</v>
+        <v>1.3576</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.7216</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.0595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ELOLA AGUIRREZABALA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0114</v>
+        <v>-1.5169</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2112</v>
+        <v>-3.9229</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2226</v>
+        <v>2.4059</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5319</v>
+        <v>6.4597</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3461</v>
+        <v>-2.722</v>
       </c>
       <c r="I7" t="n">
-        <v>0.878</v>
+        <v>9.181699999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.24</v>
+        <v>7.635000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04</v>
+        <v>0.03660000000000008</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>7.5984</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2919</v>
+        <v>-1.1754</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3861</v>
+        <v>-2.7586</v>
       </c>
       <c r="O7" t="n">
-        <v>0.678</v>
+        <v>1.5834</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2001</v>
+        <v>-8.179</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-16.163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2001</v>
+        <v>7.9843</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1991</v>
+        <v>-3.4987</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4512</v>
+        <v>-2.5149</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6503</v>
+        <v>-0.9839</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0803</v>
+        <v>3.7012</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>7.1201</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0803</v>
+        <v>-3.419</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.468</v>
+        <v>-2.7425</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1383000000000001</v>
+        <v>-3.2944</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1144</v>
+        <v>1.8465</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5177</v>
+        <v>-1.0523</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5967</v>
+        <v>2.8989</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3767</v>
+        <v>2.7577</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0418</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3349</v>
+        <v>1.98</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2622</v>
+        <v>-0.9109999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4759</v>
+        <v>-1.8299</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7382</v>
+        <v>0.919</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2</v>
+        <v>2.7264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.401</v>
+        <v>-5.4526</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2009</v>
+        <v>8.179</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.0665</v>
+        <v>-6.1106</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5135</v>
+        <v>-3.6519</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.553</v>
+        <v>-2.4587</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6202</v>
+        <v>-1.2048</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3996</v>
+        <v>3.0527</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7794</v>
+        <v>-4.2574</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. OSTOLAZA OSTOLAZA</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3357</v>
+        <v>-2.9457</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-1.3288</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3357</v>
+        <v>-1.6168</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5424</v>
+        <v>1.4324</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4068</v>
+        <v>2.5379</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1356</v>
+        <v>-1.1055</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.098</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.6326</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5346000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5424</v>
+        <v>-0.6656</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4068</v>
+        <v>-0.09460000000000002</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1356</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>-3.5053</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.868399999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2001</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4068</v>
+        <v>-1.8145</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1.2801</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4068</v>
+        <v>-0.5344</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9414999999999998</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.7216</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.7801</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>E. JUARROS CASTANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-4.0893</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7878999999999998</v>
+        <v>-1.6542</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0242</v>
+        <v>-2.4351</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8922</v>
+        <v>-0.8003</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2494000000000001</v>
+        <v>0.5013</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6428</v>
+        <v>-1.3016</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.05449999999999999</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3345</v>
+        <v>0.7184</v>
       </c>
       <c r="L10" t="n">
-        <v>0.28</v>
+        <v>-0.0727</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9468</v>
+        <v>-1.446</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5839000000000001</v>
+        <v>-0.2171</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3629</v>
+        <v>-1.2289</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0444</v>
+        <v>-0.7048</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2672</v>
+        <v>-0.1578</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3116</v>
+        <v>-0.547</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4596</v>
+        <v>-1.2211</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4596</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>X. OSTOLAZA OSTOLAZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8757</v>
+        <v>-4.8734</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3818</v>
+        <v>-5.7296</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4939</v>
+        <v>0.8562000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5863</v>
+        <v>-0.009100000000000108</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7483</v>
+        <v>3.2491</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1618999999999999</v>
+        <v>-3.2582</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4737</v>
+        <v>-0.01319999999999988</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7668</v>
+        <v>2.4016</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2931</v>
+        <v>-2.4149</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1126</v>
+        <v>0.004199999999999982</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01869999999999994</v>
+        <v>0.8475</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1313</v>
+        <v>-0.8433999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2004</v>
+        <v>-1.1685</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4007</v>
+        <v>-3.8947</v>
       </c>
       <c r="R11" t="n">
-        <v>3.601</v>
+        <v>2.7262</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.7495</v>
+        <v>-2.0217</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8867</v>
+        <v>-1.4905</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8628</v>
+        <v>-0.5312</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2598</v>
+        <v>-1.6743</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3792</v>
+        <v>-0.3311</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1195</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0633</v>
+        <v>-5.474299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7736</v>
+        <v>-1.2578</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2897</v>
+        <v>-4.2164</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4628</v>
+        <v>3.7505</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5582</v>
+        <v>0.9226000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0954</v>
+        <v>2.8279</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9087</v>
+        <v>3.2249</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5029</v>
+        <v>2.0658</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5942</v>
+        <v>1.1591</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.446</v>
+        <v>0.5255999999999996</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05530000000000002</v>
+        <v>-1.1432</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5012000000000001</v>
+        <v>1.6686</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.601</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.0014</v>
+        <v>-3.8948</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4004</v>
+        <v>3.8947</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.865</v>
+        <v>-1.5676</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3403</v>
+        <v>0.1255999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.6931</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9400000000000002</v>
+        <v>-7.6573</v>
       </c>
       <c r="W12" t="n">
-        <v>2.6593</v>
+        <v>-0.7137</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7194</v>
+        <v>-6.9437</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTANO</t>
+          <t>M. LARRANAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1245</v>
+        <v>-8.246600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7903</v>
+        <v>-11.491</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3342</v>
+        <v>3.2444</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7955</v>
+        <v>-2.6522</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5068</v>
+        <v>-0.9393</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3023</v>
+        <v>-1.7128</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5836</v>
+        <v>-3.5354</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6998</v>
+        <v>-0.2539</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1162</v>
+        <v>-3.2814</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3791</v>
+        <v>0.8833</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.193</v>
+        <v>-0.6854</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1861</v>
+        <v>1.5685</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4004</v>
+        <v>-4.2841</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2006</v>
+        <v>-7.7895</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8002</v>
+        <v>3.5053</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7288</v>
+        <v>-1.6414</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1733</v>
+        <v>-1.6667</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5555</v>
+        <v>0.02550000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1998</v>
+        <v>0.331</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1998</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.657</v>
+        <v>-9.477900000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.7496</v>
+        <v>-9.0596</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0926</v>
+        <v>-0.4184000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1123</v>
+        <v>-1.3531</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1744999999999999</v>
+        <v>0.6357000000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2867999999999999</v>
+        <v>-1.9887</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.3304</v>
+        <v>0.7815000000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6162</v>
+        <v>0.5931999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7142000000000001</v>
+        <v>0.1883999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2181</v>
+        <v>-2.1346</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7907</v>
+        <v>0.04250000000000004</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4274</v>
+        <v>-2.1771</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.8008</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.0012</v>
+        <v>-8.3736</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2004</v>
+        <v>7.7895</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.744</v>
+        <v>-7.4184</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.418</v>
+        <v>-4.1374</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3259</v>
+        <v>-3.2811</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.1220999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.6701</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.7562</v>
+        <v>-10.7593</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.0071</v>
+        <v>-14.5485</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7491</v>
+        <v>3.7891</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9167000000000001</v>
+        <v>-3.7708</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1881</v>
+        <v>0.2692999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1048</v>
+        <v>-4.0401</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9785</v>
+        <v>-4.6438</v>
       </c>
       <c r="K15" t="n">
-        <v>0.278</v>
+        <v>-1.0877</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7006</v>
+        <v>-3.5561</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0618</v>
+        <v>0.8729</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4661</v>
+        <v>1.3569</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5957</v>
+        <v>-0.484</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.0017</v>
+        <v>-0.9737000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-8.4024</v>
+        <v>-5.8421</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4007</v>
+        <v>4.8684</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5107</v>
+        <v>-4.6363</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2223</v>
+        <v>-4.0627</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2884</v>
+        <v>-0.5737</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1606</v>
+        <v>-1.3784</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6391</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7997</v>
+        <v>-1.3784</v>
       </c>
     </row>
     <row r="16">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>7.252800000000001</v>
+        <v>-28.4434</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1378999999999984</v>
+        <v>-42.1539</v>
       </c>
       <c r="F16" t="n">
-        <v>7.114899999999999</v>
+        <v>13.7102</v>
       </c>
       <c r="G16" t="n">
-        <v>18.20359999999999</v>
+        <v>18.2636</v>
       </c>
       <c r="H16" t="n">
-        <v>8.848599999999999</v>
+        <v>12.751</v>
       </c>
       <c r="I16" t="n">
-        <v>9.354899999999997</v>
+        <v>5.512899999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>18.4229</v>
+        <v>23.4937</v>
       </c>
       <c r="K16" t="n">
-        <v>6.8705</v>
+        <v>18.195</v>
       </c>
       <c r="L16" t="n">
-        <v>11.5526</v>
+        <v>5.298699999999998</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2192999999999998</v>
+        <v>-5.23</v>
       </c>
       <c r="N16" t="n">
-        <v>1.978199999999999</v>
+        <v>-5.4438</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1976</v>
+        <v>0.2138</v>
       </c>
       <c r="P16" t="n">
-        <v>-11.0029</v>
+        <v>-14.6053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-33.0095</v>
+        <v>-74.9735</v>
       </c>
       <c r="R16" t="n">
-        <v>22.0064</v>
+        <v>60.3683</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.167799999999999</v>
+        <v>-14.5728</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9694999999999989</v>
+        <v>-10.4003</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.137099999999999</v>
+        <v>-4.1725</v>
       </c>
       <c r="V16" t="n">
-        <v>2.22</v>
+        <v>-17.5292</v>
       </c>
       <c r="W16" t="n">
-        <v>13.7549</v>
+        <v>19.7267</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.535</v>
+        <v>-37.2559</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ULACIA ZKE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ULACIA ZKE.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>13.7397</v>
+        <v>7.2483</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0626</v>
+        <v>-0.1375999999999998</v>
       </c>
       <c r="F2" t="n">
-        <v>9.677099999999999</v>
+        <v>7.386</v>
       </c>
       <c r="G2" t="n">
         <v>6.872400000000001</v>
@@ -610,13 +610,13 @@
         <v>8.178900000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>9.941700000000001</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>5.1658</v>
+        <v>0.9654999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>4.7758</v>
+        <v>2.4845</v>
       </c>
       <c r="V2" t="n">
         <v>-3.8532</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4067</v>
+        <v>3.0632</v>
       </c>
       <c r="E3" t="n">
-        <v>1.226799999999999</v>
+        <v>3.0632</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1799</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1918</v>
+        <v>3.0632</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7788</v>
+        <v>1.8474</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5870999999999998</v>
+        <v>1.2158</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3014999999999999</v>
+        <v>3.0632</v>
       </c>
       <c r="K3" t="n">
-        <v>1.435</v>
+        <v>1.8474</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1336</v>
+        <v>1.2158</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8902000000000001</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3439000000000001</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5464</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-8.179</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6.6211</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5408</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.153799999999999</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3871</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.768</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5.9506</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.7185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0632</v>
+        <v>0.9830000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0632</v>
+        <v>2.0761</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.0931</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0632</v>
+        <v>0.944</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8474</v>
+        <v>2.5067</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2158</v>
+        <v>-1.5626</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0632</v>
+        <v>1.8096</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8474</v>
+        <v>2.2631</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2158</v>
+        <v>-0.4536</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.8655</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1.1091</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.5905</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.01289999999999997</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.5776</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.9021</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6414</v>
+        <v>0.9603000000000005</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2722</v>
+        <v>-0.8402999999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.631</v>
+        <v>1.8007</v>
       </c>
       <c r="G5" t="n">
-        <v>0.944</v>
+        <v>1.8465</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5067</v>
+        <v>-1.0523</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5626</v>
+        <v>2.8989</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8096</v>
+        <v>2.7577</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2631</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4536</v>
+        <v>1.98</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8655</v>
+        <v>-0.9109999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2436</v>
+        <v>-1.8299</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1091</v>
+        <v>0.919</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5315</v>
+        <v>2.7264</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-5.4526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5315</v>
+        <v>8.179</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06790000000000007</v>
+        <v>-2.4078</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1833</v>
+        <v>-1.1979</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1154</v>
+        <v>-1.2099</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9021</v>
+        <v>-1.2048</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2795</v>
+        <v>3.0527</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1816</v>
+        <v>-4.2574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ELOLA AGUIRREZABALA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1685</v>
+        <v>0.8955999999999995</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4919</v>
+        <v>-2.4656</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3234</v>
+        <v>3.3611</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2886</v>
+        <v>6.4597</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4411999999999999</v>
+        <v>-2.722</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8473999999999999</v>
+        <v>9.181699999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2107</v>
+        <v>7.635000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8621</v>
+        <v>0.03660000000000008</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3486</v>
+        <v>7.5984</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07779999999999998</v>
+        <v>-1.1754</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.421</v>
+        <v>-2.7586</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4988</v>
+        <v>1.5834</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9737</v>
+        <v>-8.179</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9737</v>
+        <v>-16.163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9473</v>
+        <v>7.9843</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2908</v>
+        <v>-1.0863</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0668</v>
+        <v>-1.0577</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3576</v>
+        <v>-0.02869999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.7216</v>
+        <v>3.7012</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6621</v>
+        <v>7.1201</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.0595</v>
+        <v>-3.419</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>P. ELOLA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5169</v>
+        <v>-0.06579999999999986</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.9229</v>
+        <v>-0.9934000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4059</v>
+        <v>0.9276</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4597</v>
+        <v>1.2886</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.722</v>
+        <v>0.4411999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>9.181699999999999</v>
+        <v>0.8473999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>7.635000000000001</v>
+        <v>1.2107</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03660000000000008</v>
+        <v>0.8621</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5984</v>
+        <v>0.3486</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1754</v>
+        <v>0.07779999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.7586</v>
+        <v>-0.421</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5834</v>
+        <v>0.4988</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.179</v>
+        <v>0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.163</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>7.9843</v>
+        <v>1.9473</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.4987</v>
+        <v>0.3933</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.5149</v>
+        <v>-0.5685</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9839</v>
+        <v>0.9619</v>
       </c>
       <c r="V7" t="n">
-        <v>3.7012</v>
+        <v>-2.7216</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1201</v>
+        <v>-0.6621</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.419</v>
+        <v>-2.0595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7425</v>
+        <v>-0.2454000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2944</v>
+        <v>-1.9767</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.7313</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8465</v>
+        <v>1.1918</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0523</v>
+        <v>1.7788</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8989</v>
+        <v>-0.5870999999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7577</v>
+        <v>0.3014999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.435</v>
       </c>
       <c r="L8" t="n">
-        <v>1.98</v>
+        <v>-1.1336</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9109999999999999</v>
+        <v>0.8902000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8299</v>
+        <v>0.3439000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.919</v>
+        <v>0.5464</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7264</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.4526</v>
+        <v>-8.179</v>
       </c>
       <c r="R8" t="n">
-        <v>8.179</v>
+        <v>6.6211</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.1106</v>
+        <v>0.8888</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.6519</v>
+        <v>-0.04960000000000003</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.4587</v>
+        <v>0.9385</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2048</v>
+        <v>-0.768</v>
       </c>
       <c r="W8" t="n">
-        <v>3.0527</v>
+        <v>5.9506</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.2574</v>
+        <v>-6.7185</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9457</v>
+        <v>-1.5253</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3288</v>
+        <v>-0.7308</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6168</v>
+        <v>-0.7945</v>
       </c>
       <c r="G9" t="n">
         <v>1.4324</v>
@@ -1156,13 +1156,13 @@
         <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8145</v>
+        <v>-0.3941</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2801</v>
+        <v>-0.6819999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5344</v>
+        <v>0.288</v>
       </c>
       <c r="V9" t="n">
         <v>0.9414999999999998</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0893</v>
+        <v>-3.5075</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6542</v>
+        <v>-1.1558</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4351</v>
+        <v>-2.3517</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8003</v>
@@ -1234,13 +1234,13 @@
         <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7048</v>
+        <v>-0.123</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1578</v>
+        <v>0.3406</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.547</v>
+        <v>-0.4635</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2211</v>
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8734</v>
+        <v>-3.6803</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7296</v>
+        <v>-5.2072</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8562000000000001</v>
+        <v>1.5269</v>
       </c>
       <c r="G11" t="n">
         <v>-0.009100000000000108</v>
@@ -1312,13 +1312,13 @@
         <v>2.7262</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0217</v>
+        <v>-0.8286</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4905</v>
+        <v>-0.9681</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5312</v>
+        <v>0.1395</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6743</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.474299999999999</v>
+        <v>-4.802</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2578</v>
+        <v>-6.705</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2164</v>
+        <v>1.9032</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7505</v>
+        <v>-1.3531</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9226000000000001</v>
+        <v>0.6357000000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8279</v>
+        <v>-1.9887</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2249</v>
+        <v>0.7815000000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>2.0658</v>
+        <v>0.5931999999999998</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1591</v>
+        <v>0.1883999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5255999999999996</v>
+        <v>-2.1346</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1432</v>
+        <v>0.04250000000000004</v>
       </c>
       <c r="O12" t="n">
-        <v>1.6686</v>
+        <v>-2.1771</v>
       </c>
       <c r="P12" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8948</v>
+        <v>-8.3736</v>
       </c>
       <c r="R12" t="n">
-        <v>3.8947</v>
+        <v>7.7895</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5676</v>
+        <v>-2.7425</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1255999999999999</v>
+        <v>-1.783</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6931</v>
+        <v>-0.9594999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.6573</v>
+        <v>-0.1220999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7137</v>
+        <v>2.6701</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.9437</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. LARRANAGA ORMAZABAL</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.246600000000001</v>
+        <v>-5.236800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.491</v>
+        <v>-2.5536</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2444</v>
+        <v>-2.6833</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6522</v>
+        <v>3.7505</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9393</v>
+        <v>0.9226000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7128</v>
+        <v>2.8279</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.5354</v>
+        <v>3.2249</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2539</v>
+        <v>2.0658</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2814</v>
+        <v>1.1591</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8833</v>
+        <v>0.5255999999999996</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6854</v>
+        <v>-1.1432</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5685</v>
+        <v>1.6686</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.2841</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.7895</v>
+        <v>-3.8948</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5053</v>
+        <v>3.8947</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6414</v>
+        <v>-1.3298</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6667</v>
+        <v>-1.1702</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02550000000000001</v>
+        <v>-0.1596</v>
       </c>
       <c r="V13" t="n">
-        <v>0.331</v>
+        <v>-7.6573</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5005</v>
+        <v>-0.7137</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1695</v>
+        <v>-6.9437</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>M. LARRANAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.477900000000002</v>
+        <v>-6.3278</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.0596</v>
+        <v>-10.2709</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4184000000000001</v>
+        <v>3.943</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3531</v>
+        <v>-2.6522</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6357000000000002</v>
+        <v>-0.9393</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9887</v>
+        <v>-1.7128</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7815000000000002</v>
+        <v>-3.5354</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5931999999999998</v>
+        <v>-0.2539</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1883999999999999</v>
+        <v>-3.2814</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1346</v>
+        <v>0.8833</v>
       </c>
       <c r="N14" t="n">
-        <v>0.04250000000000004</v>
+        <v>-0.6854</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1771</v>
+        <v>1.5685</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-4.2841</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.3736</v>
+        <v>-7.7895</v>
       </c>
       <c r="R14" t="n">
-        <v>7.7895</v>
+        <v>3.5053</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.4184</v>
+        <v>0.2774</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.1374</v>
+        <v>-0.4466</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.2811</v>
+        <v>0.7239</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1220999999999999</v>
+        <v>0.331</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6701</v>
+        <v>1.5005</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7922</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.7593</v>
+        <v>-8.6305</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.5485</v>
+        <v>-13.3283</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7891</v>
+        <v>4.698</v>
       </c>
       <c r="G15" t="n">
         <v>-3.7708</v>
@@ -1624,13 +1624,13 @@
         <v>4.8684</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.6363</v>
+        <v>-2.5076</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.0627</v>
+        <v>-2.8425</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5737</v>
+        <v>0.335</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3784</v>
@@ -1657,22 +1657,22 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-28.4434</v>
+        <v>-20.871</v>
       </c>
       <c r="E16" t="n">
-        <v>-42.1539</v>
+        <v>-41.2259</v>
       </c>
       <c r="F16" t="n">
-        <v>13.7102</v>
+        <v>20.3552</v>
       </c>
       <c r="G16" t="n">
-        <v>18.2636</v>
+        <v>18.26359999999999</v>
       </c>
       <c r="H16" t="n">
         <v>12.751</v>
       </c>
       <c r="I16" t="n">
-        <v>5.512899999999999</v>
+        <v>5.512899999999997</v>
       </c>
       <c r="J16" t="n">
         <v>23.4937</v>
@@ -1690,25 +1690,25 @@
         <v>-5.4438</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2138</v>
+        <v>0.2138000000000002</v>
       </c>
       <c r="P16" t="n">
         <v>-14.6053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-74.9735</v>
+        <v>-74.97350000000002</v>
       </c>
       <c r="R16" t="n">
         <v>60.3683</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.5728</v>
+        <v>-7.0007</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.4003</v>
+        <v>-9.472899999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.1725</v>
+        <v>2.472499999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-17.5292</v>
